--- a/data/2026/Programok.xlsx
+++ b/data/2026/Programok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zokinczl/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D05811-8F5E-3241-96D4-338C571F99E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29754C3C-0900-8E4C-8AAA-DDBB6034C9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="18880" xr2:uid="{9DA275EA-76A4-C34E-8EE0-63355927C542}"/>
+    <workbookView xWindow="2420" yWindow="900" windowWidth="28040" windowHeight="18880" xr2:uid="{9DA275EA-76A4-C34E-8EE0-63355927C542}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1658,10 +1658,10 @@
         <v>70</v>
       </c>
       <c r="D48" s="2">
-        <v>0.75</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
